--- a/TESTS/zlit_7_haul.xlsx
+++ b/TESTS/zlit_7_haul.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Діана Вінн Джонс — британська письменниця майстер фентезі для підлітків</t>
+          <t>Діана Вінн Джонс</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Фентезі — твір у вигаданому чарівному світі з магією чарівниками і неймовірними пригодами</t>
+          <t>Фентезі</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Фентезі може досліджувати складні людські теми — самоприйняття, ідентичність, страх і любов — через магічні метафори</t>
+          <t>Фентезі може досліджувати складні людські теми</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Софі — старша з трьох сестер що не вірить у власну цінність бо «перша сестра ніколи не матиме успіху»</t>
+          <t>Софі</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Перетворює Софі на дуже стару жінку — вона вимушена залишити дім і шукати порятунку</t>
+          <t>Перетворює Софі на дуже стару жінку</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Глибока впевненість у власній нецікавості і другорядності — вона роками приховувала власний потенціал</t>
+          <t>Глибока впевненість у власній нецікавості і другорядності</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Красивий могутній чарівник зі скандальною репутацією — мовляв поїдає серця молодих дівчат</t>
+          <t>Красивий могутній чарівник зі скандальною репутацією</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -897,6 +937,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Вогняний демон що уклав угоду з Хаулом і живить замок — хитрий але добрий союзник Софі</t>
+          <t>Вогняний демон що уклав угоду з Хаулом і живить замок</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Чим займалась Софі до зустрічі з Відьмою Пустошей?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Навчалась магії</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Працювала в крамниці капелюхів свого батька, вважаючи себе нецікавою і приреченою на буденність</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Мандрувала</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Служила при дворі</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Чому Відьма Пустошей звернула увагу на Софі і наклала прокляття саме на неї?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Випадково помилилась</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Побачила Хаула поряд із Софі і позаздрила через суперницю, що загрожувала її плану заволодіти Хаулом</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Хаул попросив прокляти Софі</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо Софі сама образила відьму</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Що особливо парадоксально у проклятті Відьми для Софі?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Воно не мало ніякого ефекту</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ставши старою, Софі почала поводитись вільніше і впевненіше, ніж будь-коли у молодості</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Воно зробило її невидимою</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Воно посилило її магію</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Як Софі опинилась усередині Мандрівного замку Хаула?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Хаул запросив її</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Прийшла сама в ніч після прокляття, сподіваючись знайти допомогу або хоч дах над головою</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Замок сам підібрав її</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона заблукала і потрапила випадково</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Хто зустрів Софі всередині замку першим?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сам Хаул</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Кальцифер — вогняний демон, що горів у каміні і вів замок</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Учень Хаула Майкл</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ніхто — замок був порожній</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Яку угоду запропонувала Софі Кальциферу при першій зустрічі?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого не запропонувала</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Зняти прокляття з неї в обмін на звільнення його від контракту з Хаулом</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Готувати йому їжу</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Стати його слугою</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Скільки різних виходів-порталів мав Мандрівний замок Хаула?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Один</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Чотири — кожен відкривався в інше місто чи місце в залежності від кольору засувки</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Два</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Без лічби — безмежно багато</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Чому Мандрівний замок мав потребу весь час рухатися?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Хаул любив подорожі</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Щоб Відьма Пустошей та інші вороги не могли точно знайти і заблокувати його</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Так дешевше за оренду</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Його змушував Кальцифер</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Яке враження Мандрівний замок справляв на людей ззовні?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Красивий і привабливий</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Похмурий і страхітливий — задимлений, рухомий на механічних ногах, наганяв жах на мешканців</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Непомітний і невидимий</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Маленький і тихий</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Яку репутацію мав Хаул серед мешканців міста?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Добродійника і рятівника</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>«Пожирача сердець» — розповідали, що він зваблює дівчат і поглинає їхні душі</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Самітного вченого</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Доброго придворного чарівника</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Чим насправді займався Хаул замість «поглинання сердець»?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Злочинами</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Після розлучення залицявся до дівчат, не знаходив відповіді на своє самотнє серце і тікав від стосунків</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Зачаровував ворогів</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Писав заклинання для короля</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Що відбувалось із Хаулом, коли хтось різко критикував його зовнішність?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він ігнорував це</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Влаштовував драматичні сцени — «помирав» від жаху, заганяв слиз у водостоки</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ставав злим</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ставав холодним і жорстоким</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Яку таємну угоду уклав Хаул з Кальциферем давним-давно?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Подарував Кальциферу замок</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Віддав Кальциферу своє серце, щоб той отримав силу й жив — але це зробило Хаула безсердечнішим</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Отримав від Кальцифера магію</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Обміняв серце на безсмертя</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Як відсутність серця впливала на характер Хаула?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого не змінило</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Робила його поверховим, безвідповідальним, нездатним на справжню відданість і стосунки</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Зробила його жорстоким злодієм</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Дала йому надсилу</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Що мала зробити Софі, щоб зламати пов'язане закляття Хаула-Кальцифера?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Заспівати магічну пісню</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>З'ясувати, як вони пов'язані, і допомогти їм обом звільнитись одному від одного</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Знайти книгу заклинань</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Попросити Відьму</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Що сталося з Відьмою Пустошей наприкінці роману?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вона перемогла Хаула</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона втратила свою силу і повернулась до вигляду простої старенької</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона зникла безслідно</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона помирилась з Хаулом і стала союзником</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Як Хаул і Кальцифер звільнились від своєї угоди?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Кальцифер сам відмовився</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Завдяки Софі, яка зрозуміла природу їхнього зв'язку і відновила серце Хаула</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Угода скінчилась автоматично</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Відьма розірвала угоду</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Чим закінчується внутрішня трансформація Хаула до кінця роману?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він залишається таким самим</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він стає здатним до справжнього кохання й відповідальності, зізнавшись Софі в почуттях</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він залишає всіх і живе самотньо</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він стає слугою короля</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Яку трансформацію переживає Софі паралельно із зовнішньою зміною?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лише зовнішню</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Внутрішню — вона поступово відкриває власну цінність і магію, перестаючи бачити себе «другорядною»</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона стає жорстокою</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона залишається пасивною до кінця</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Як прокляття Відьми парадоксально допомогло Софі?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ніяк не допомогло</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Звільнило від самоцензури і страху — у вигляді старої вона могла говорити і діяти так, як ніколи раніше</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дало їй магію</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Зробило її невидимою для ворогів</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Яку головну думку роман Діани Вінн Джонс передає читачу через долю Софі і Хаула?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Магія важливіша за характер</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Справжня трансформація — внутрішня: прийняти себе і навчитись відповідати за стосунки з іншими</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Зовнішня краса вирішує все</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Краще залишатись самотнім</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Чим твори Діани Вінн Джонс відрізняються від типового фентезі?</t>
+          <t>Діана Вінн Джонс відрізняється від типового фентезі тим, що поєднує пригоди з психологічно глибокими персонажами і гумором.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,29 +2133,32 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яку роль відіграє гумор у «Мандрівному замку Хаула»?</t>
+          <t>Гумор у «Мандрівному замку Хаула» слугує лише розвагою і не несе жодного змістового навантаження.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Що спільного між «Мандрівним замком Хаула» і «Алісою в Країні Див»?</t>
+          <t>І «Мандрівний замок Хаула», і «Аліса в Країні Див» мають спільне: несподівані правила вигаданого світу, що відображають внутрішній стан героїні.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея «Мандрівного замку Хаула»?</t>
+          <t>Головна ідея «Мандрівного замку Хаула» — прийняти себе і взяти відповідальність за стосунки важливіше, ніж зовнішні зміни.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Що об'єднує Софі і Хаула як персонажів?</t>
+          <t>Софі і Хаула об'єднує те, що обоє тікають від власної суті і від відповідальності — кожен по-своєму.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка роль теми самоприйняття у романі для підлітків?</t>
+          <t>Тема самоприйняття у «Мандрівному замку Хаула» є суто казковою і не має жодного зв'язку з реальними переживаннями підлітків.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які теми розкриває «Мандрівний замок Хаула»?</t>
+          <t>Що відбувається у романі «Мандрівний замок Хаула»?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Самоприйняття і внутрішня трансформація</t>
+          <t>Софі стає старою через прокляття Відьми</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Страх відповідальності і втеча від себе</t>
+          <t>Кальцифер і Хаул пов'язані таємною угодою про серце</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Небезпека магії</t>
+          <t>Прокляття зникло само</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Кохання що долає зовнішній вигляд</t>
+          <t>Хаул і Кальцифер звільняються завдяки Софі</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Парадоксальне звільнення — у образі старої вона нарешті дозволяє собі бути сміливою і прямолінійною</t>
+          <t>Парадоксальне звільнення</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Він пересувається чотиривимірними дверима що відкриваються у різні місця — символ меж і переходів</t>
+          <t>Він пересувається чотиривимірними дверима що відкриваються у різні місця</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Вона відкриває власну цінність і магію — і розуміє що завжди мала силу яку приховувала від себе</t>
+          <t>Вона відкриває власну цінність і магію</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
